--- a/Eurorack_MIDI-BLE_2x2/Eurorack_MIDI-BLE_2x2_bom.xlsx
+++ b/Eurorack_MIDI-BLE_2x2/Eurorack_MIDI-BLE_2x2_bom.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andrei/Documents/GitHub/Midi-boards/Eurorack_MIDI-BLE_2x2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7E501D0-2F3C-1E4A-9921-FB5808D5EF48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CD5F5FC-254B-5047-907C-96F02BA7341A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8540" yWindow="600" windowWidth="19200" windowHeight="26700" xr2:uid="{1DC00C95-4B08-F94A-83B0-76F56463D0E9}"/>
+    <workbookView xWindow="8540" yWindow="780" windowWidth="19200" windowHeight="21120" xr2:uid="{1DC00C95-4B08-F94A-83B0-76F56463D0E9}"/>
   </bookViews>
   <sheets>
     <sheet name="Eurorack MIDI BLE 2x2" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Eurorack MIDI BLE 2x2'!$A$1:$E$53</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Eurorack MIDI BLE 2x2'!$A$1:$E$52</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="716" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="713" uniqueCount="219">
   <si>
     <t>D</t>
   </si>
@@ -869,7 +869,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -885,18 +885,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1211,7 +1210,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AJ189"/>
+  <dimension ref="A1:AJ188"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22.6640625" bestFit="1" customWidth="1"/>
@@ -1273,13 +1272,13 @@
       </c>
     </row>
     <row r="2" spans="1:29" ht="31" x14ac:dyDescent="0.35">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="13" t="s">
         <v>184</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="16"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="15"/>
       <c r="R2" t="s">
         <v>2</v>
       </c>
@@ -1574,7 +1573,7 @@
       <c r="B12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C12" s="18" t="s">
+      <c r="C12" t="s">
         <v>215</v>
       </c>
       <c r="E12" s="3">
@@ -2264,13 +2263,13 @@
     <row r="35" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A35" s="3"/>
       <c r="B35" s="3" t="s">
-        <v>3</v>
+        <v>188</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>167</v>
+        <v>213</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>168</v>
+        <v>214</v>
       </c>
       <c r="E35" s="3">
         <v>1</v>
@@ -2282,11 +2281,9 @@
         <v>188</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>214</v>
-      </c>
+        <v>218</v>
+      </c>
+      <c r="D36" s="3"/>
       <c r="E36" s="3">
         <v>1</v>
       </c>
@@ -2294,12 +2291,14 @@
     <row r="37" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A37" s="3"/>
       <c r="B37" s="3" t="s">
-        <v>188</v>
+        <v>33</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D37" s="3"/>
+        <v>203</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>172</v>
+      </c>
       <c r="E37" s="3">
         <v>1</v>
       </c>
@@ -2307,61 +2306,61 @@
     <row r="38" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A38" s="3"/>
       <c r="B38" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>172</v>
+        <v>204</v>
       </c>
       <c r="E38" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A39" s="3"/>
       <c r="B39" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E39" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A40" s="3"/>
       <c r="B40" s="3" t="s">
-        <v>35</v>
+        <v>208</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>206</v>
+        <v>174</v>
       </c>
       <c r="E40" s="3">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="41" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A41" s="3"/>
       <c r="B41" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>173</v>
+        <v>216</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>174</v>
+        <v>210</v>
       </c>
       <c r="E41" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:29" x14ac:dyDescent="0.2">
@@ -2370,60 +2369,60 @@
         <v>209</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>210</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="D42" s="3"/>
       <c r="E42" s="3">
         <v>1</v>
+      </c>
+      <c r="R42" t="s">
+        <v>11</v>
+      </c>
+      <c r="S42" t="s">
+        <v>27</v>
+      </c>
+      <c r="T42">
+        <v>4</v>
+      </c>
+      <c r="V42" t="s">
+        <v>26</v>
+      </c>
+      <c r="W42" t="s">
+        <v>9</v>
+      </c>
+      <c r="X42" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y42" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="43" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A43" s="3"/>
       <c r="B43" s="3" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="D43" s="3"/>
       <c r="E43" s="3">
         <v>1</v>
-      </c>
-      <c r="R43" t="s">
-        <v>11</v>
-      </c>
-      <c r="S43" t="s">
-        <v>27</v>
-      </c>
-      <c r="T43">
-        <v>4</v>
-      </c>
-      <c r="V43" t="s">
-        <v>26</v>
-      </c>
-      <c r="W43" t="s">
-        <v>9</v>
-      </c>
-      <c r="X43" t="s">
-        <v>74</v>
-      </c>
-      <c r="Y43" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="44" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A44" s="3"/>
       <c r="B44" s="3" t="s">
-        <v>211</v>
+        <v>175</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="D44" s="3"/>
+        <v>176</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>177</v>
+      </c>
       <c r="E44" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45" spans="1:29" x14ac:dyDescent="0.2">
@@ -2432,28 +2431,36 @@
         <v>175</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E45" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A46" s="3"/>
-      <c r="B46" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="E46" s="3">
-        <v>1</v>
+      <c r="R46" t="s">
+        <v>11</v>
+      </c>
+      <c r="S46" t="s">
+        <v>27</v>
+      </c>
+      <c r="T46">
+        <v>4</v>
+      </c>
+      <c r="V46" t="s">
+        <v>26</v>
+      </c>
+      <c r="W46" t="s">
+        <v>9</v>
+      </c>
+      <c r="X46" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y46" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="47" spans="1:29" x14ac:dyDescent="0.2">
@@ -2461,25 +2468,29 @@
         <v>11</v>
       </c>
       <c r="S47" t="s">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="T47">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V47" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="W47" t="s">
         <v>9</v>
       </c>
-      <c r="X47" t="s">
-        <v>76</v>
-      </c>
-      <c r="Y47" t="s">
-        <v>27</v>
+      <c r="Z47" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="48" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A48" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="B48" s="5"/>
+      <c r="C48" s="5"/>
+      <c r="D48" s="5"/>
+      <c r="E48" s="6"/>
       <c r="R48" t="s">
         <v>11</v>
       </c>
@@ -2496,78 +2507,74 @@
         <v>9</v>
       </c>
       <c r="Z48" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="49" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A49" s="11" t="s">
-        <v>169</v>
-      </c>
-      <c r="B49" s="5"/>
-      <c r="C49" s="5"/>
-      <c r="D49" s="5"/>
-      <c r="E49" s="6"/>
-      <c r="R49" t="s">
+      <c r="A49" s="10"/>
+      <c r="E49" s="7"/>
+    </row>
+    <row r="50" spans="1:29" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="16" t="s">
+        <v>180</v>
+      </c>
+      <c r="B50" s="17"/>
+      <c r="C50" s="17"/>
+      <c r="E50" s="7"/>
+      <c r="R50" t="s">
         <v>11</v>
       </c>
-      <c r="S49" t="s">
+      <c r="S50" t="s">
         <v>0</v>
       </c>
-      <c r="T49">
+      <c r="T50">
         <v>5</v>
       </c>
-      <c r="V49" t="s">
+      <c r="V50" t="s">
         <v>14</v>
       </c>
-      <c r="W49" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z49" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="50" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A50" s="10"/>
-      <c r="E50" s="7"/>
-    </row>
-    <row r="51" spans="1:29" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="13" t="s">
-        <v>180</v>
-      </c>
-      <c r="B51" s="14"/>
-      <c r="C51" s="14"/>
-      <c r="E51" s="7"/>
+      <c r="W50" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA50" t="s">
+        <v>90</v>
+      </c>
+      <c r="AB50">
+        <v>1</v>
+      </c>
+      <c r="AC50" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="51" spans="1:29" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="12"/>
+      <c r="B51" s="8"/>
+      <c r="C51" s="8"/>
+      <c r="D51" s="8"/>
+      <c r="E51" s="9"/>
       <c r="R51" t="s">
         <v>11</v>
       </c>
       <c r="S51" t="s">
+        <v>24</v>
+      </c>
+      <c r="T51">
+        <v>7</v>
+      </c>
+      <c r="V51" t="s">
+        <v>23</v>
+      </c>
+      <c r="W51" t="s">
+        <v>9</v>
+      </c>
+      <c r="X51" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y51" t="s">
         <v>0</v>
       </c>
-      <c r="T51">
-        <v>5</v>
-      </c>
-      <c r="V51" t="s">
-        <v>14</v>
-      </c>
-      <c r="W51" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA51" t="s">
-        <v>90</v>
-      </c>
-      <c r="AB51">
-        <v>1</v>
-      </c>
-      <c r="AC51" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="52" spans="1:29" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="12"/>
-      <c r="B52" s="8"/>
-      <c r="C52" s="8"/>
-      <c r="D52" s="8"/>
-      <c r="E52" s="9"/>
+    </row>
+    <row r="52" spans="1:29" x14ac:dyDescent="0.2">
       <c r="R52" t="s">
         <v>11</v>
       </c>
@@ -2584,10 +2591,10 @@
         <v>9</v>
       </c>
       <c r="X52" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Y52" t="s">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="53" spans="1:29" x14ac:dyDescent="0.2">
@@ -2606,11 +2613,8 @@
       <c r="W53" t="s">
         <v>9</v>
       </c>
-      <c r="X53" t="s">
-        <v>76</v>
-      </c>
-      <c r="Y53" t="s">
-        <v>24</v>
+      <c r="Z53" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="54" spans="1:29" x14ac:dyDescent="0.2">
@@ -2629,8 +2633,14 @@
       <c r="W54" t="s">
         <v>9</v>
       </c>
-      <c r="Z54" t="s">
-        <v>92</v>
+      <c r="AA54" t="s">
+        <v>91</v>
+      </c>
+      <c r="AB54">
+        <v>2</v>
+      </c>
+      <c r="AC54" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="55" spans="1:29" x14ac:dyDescent="0.2">
@@ -2638,25 +2648,22 @@
         <v>11</v>
       </c>
       <c r="S55" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="T55">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V55" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="W55" t="s">
         <v>9</v>
       </c>
-      <c r="AA55" t="s">
-        <v>91</v>
-      </c>
-      <c r="AB55">
-        <v>2</v>
-      </c>
-      <c r="AC55" t="s">
-        <v>86</v>
+      <c r="X55" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y55" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="56" spans="1:29" x14ac:dyDescent="0.2">
@@ -2676,7 +2683,7 @@
         <v>9</v>
       </c>
       <c r="X56" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Y56" t="s">
         <v>12</v>
@@ -2698,11 +2705,8 @@
       <c r="W57" t="s">
         <v>9</v>
       </c>
-      <c r="X57" t="s">
-        <v>76</v>
-      </c>
-      <c r="Y57" t="s">
-        <v>12</v>
+      <c r="Z57" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="58" spans="1:29" x14ac:dyDescent="0.2">
@@ -2721,8 +2725,14 @@
       <c r="W58" t="s">
         <v>9</v>
       </c>
-      <c r="Z58" t="s">
-        <v>93</v>
+      <c r="AA58" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB58">
+        <v>1</v>
+      </c>
+      <c r="AC58" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="59" spans="1:29" x14ac:dyDescent="0.2">
@@ -2745,7 +2755,7 @@
         <v>9</v>
       </c>
       <c r="AB59">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC59" t="s">
         <v>86</v>
@@ -2753,28 +2763,22 @@
     </row>
     <row r="60" spans="1:29" x14ac:dyDescent="0.2">
       <c r="R60" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="S60" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="T60">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="U60" t="s">
+        <v>94</v>
       </c>
       <c r="V60" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="W60" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA60" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB60">
-        <v>2</v>
-      </c>
-      <c r="AC60" t="s">
-        <v>86</v>
+        <v>4</v>
       </c>
     </row>
     <row r="61" spans="1:29" x14ac:dyDescent="0.2">
@@ -2787,14 +2791,17 @@
       <c r="T61">
         <v>9</v>
       </c>
-      <c r="U61" t="s">
-        <v>94</v>
-      </c>
       <c r="V61" t="s">
         <v>5</v>
       </c>
       <c r="W61" t="s">
         <v>4</v>
+      </c>
+      <c r="X61" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y61" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="62" spans="1:29" x14ac:dyDescent="0.2">
@@ -2814,10 +2821,10 @@
         <v>4</v>
       </c>
       <c r="X62" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Y62" t="s">
-        <v>75</v>
+        <v>7</v>
       </c>
     </row>
     <row r="63" spans="1:29" x14ac:dyDescent="0.2">
@@ -2836,11 +2843,8 @@
       <c r="W63" t="s">
         <v>4</v>
       </c>
-      <c r="X63" t="s">
-        <v>76</v>
-      </c>
-      <c r="Y63" t="s">
-        <v>7</v>
+      <c r="Z63" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="64" spans="1:29" x14ac:dyDescent="0.2">
@@ -2860,7 +2864,7 @@
         <v>4</v>
       </c>
       <c r="Z64" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="65" spans="18:29" x14ac:dyDescent="0.2">
@@ -2879,8 +2883,14 @@
       <c r="W65" t="s">
         <v>4</v>
       </c>
-      <c r="Z65" t="s">
-        <v>96</v>
+      <c r="AA65" t="s">
+        <v>97</v>
+      </c>
+      <c r="AB65">
+        <v>1</v>
+      </c>
+      <c r="AC65" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="66" spans="18:29" x14ac:dyDescent="0.2">
@@ -2900,13 +2910,13 @@
         <v>4</v>
       </c>
       <c r="AA66" t="s">
-        <v>97</v>
+        <v>43</v>
       </c>
       <c r="AB66">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC66" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
     </row>
     <row r="67" spans="18:29" x14ac:dyDescent="0.2">
@@ -2926,10 +2936,10 @@
         <v>4</v>
       </c>
       <c r="AA67" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="AB67">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC67" t="s">
         <v>86</v>
@@ -2952,13 +2962,13 @@
         <v>4</v>
       </c>
       <c r="AA68" t="s">
-        <v>48</v>
+        <v>97</v>
       </c>
       <c r="AB68">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AC68" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
     </row>
     <row r="69" spans="18:29" x14ac:dyDescent="0.2">
@@ -2978,13 +2988,13 @@
         <v>4</v>
       </c>
       <c r="AA69" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="AB69">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC69" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
     </row>
     <row r="70" spans="18:29" x14ac:dyDescent="0.2">
@@ -3004,10 +3014,10 @@
         <v>4</v>
       </c>
       <c r="AA70" t="s">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="AB70">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC70" t="s">
         <v>86</v>
@@ -3030,10 +3040,10 @@
         <v>4</v>
       </c>
       <c r="AA71" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AB71">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC71" t="s">
         <v>86</v>
@@ -3056,10 +3066,10 @@
         <v>4</v>
       </c>
       <c r="AA72" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="AB72">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC72" t="s">
         <v>86</v>
@@ -3067,28 +3077,25 @@
     </row>
     <row r="73" spans="18:29" x14ac:dyDescent="0.2">
       <c r="R73" t="s">
-        <v>6</v>
+        <v>56</v>
       </c>
       <c r="S73" t="s">
-        <v>7</v>
+        <v>57</v>
       </c>
       <c r="T73">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V73" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="W73" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA73" t="s">
-        <v>82</v>
-      </c>
-      <c r="AB73">
-        <v>8</v>
-      </c>
-      <c r="AC73" t="s">
-        <v>86</v>
+        <v>52</v>
+      </c>
+      <c r="X73" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y73" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="74" spans="18:29" x14ac:dyDescent="0.2">
@@ -3108,10 +3115,10 @@
         <v>52</v>
       </c>
       <c r="X74" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Y74" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
     </row>
     <row r="75" spans="18:29" x14ac:dyDescent="0.2">
@@ -3131,10 +3138,10 @@
         <v>52</v>
       </c>
       <c r="X75" t="s">
-        <v>76</v>
+        <v>101</v>
       </c>
       <c r="Y75" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
     </row>
     <row r="76" spans="18:29" x14ac:dyDescent="0.2">
@@ -3154,10 +3161,10 @@
         <v>52</v>
       </c>
       <c r="X76" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="Y76" t="s">
-        <v>102</v>
+        <v>52</v>
       </c>
     </row>
     <row r="77" spans="18:29" x14ac:dyDescent="0.2">
@@ -3177,10 +3184,10 @@
         <v>52</v>
       </c>
       <c r="X77" t="s">
-        <v>103</v>
+        <v>62</v>
       </c>
       <c r="Y77" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
     </row>
     <row r="78" spans="18:29" x14ac:dyDescent="0.2">
@@ -3200,10 +3207,10 @@
         <v>52</v>
       </c>
       <c r="X78" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="Y78" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="79" spans="18:29" x14ac:dyDescent="0.2">
@@ -3223,10 +3230,10 @@
         <v>52</v>
       </c>
       <c r="X79" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="Y79" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="80" spans="18:29" x14ac:dyDescent="0.2">
@@ -3246,10 +3253,10 @@
         <v>52</v>
       </c>
       <c r="X80" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="Y80" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
     </row>
     <row r="81" spans="18:36" x14ac:dyDescent="0.2">
@@ -3269,10 +3276,10 @@
         <v>52</v>
       </c>
       <c r="X81" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="Y81" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
     </row>
     <row r="82" spans="18:36" x14ac:dyDescent="0.2">
@@ -3292,10 +3299,10 @@
         <v>52</v>
       </c>
       <c r="X82" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Y82" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
     </row>
     <row r="83" spans="18:36" x14ac:dyDescent="0.2">
@@ -3315,10 +3322,10 @@
         <v>52</v>
       </c>
       <c r="X83" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="Y83" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="84" spans="18:36" x14ac:dyDescent="0.2">
@@ -3338,10 +3345,10 @@
         <v>52</v>
       </c>
       <c r="X84" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="Y84" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
     </row>
     <row r="85" spans="18:36" x14ac:dyDescent="0.2">
@@ -3361,10 +3368,10 @@
         <v>52</v>
       </c>
       <c r="X85" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="Y85" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="86" spans="18:36" x14ac:dyDescent="0.2">
@@ -3383,11 +3390,14 @@
       <c r="W86" t="s">
         <v>52</v>
       </c>
-      <c r="X86" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y86" t="s">
-        <v>70</v>
+      <c r="AA86" t="s">
+        <v>104</v>
+      </c>
+      <c r="AB86">
+        <v>1</v>
+      </c>
+      <c r="AC86" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="87" spans="18:36" x14ac:dyDescent="0.2">
@@ -3407,10 +3417,10 @@
         <v>52</v>
       </c>
       <c r="AA87" t="s">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="AB87">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC87" t="s">
         <v>81</v>
@@ -3433,79 +3443,70 @@
         <v>52</v>
       </c>
       <c r="AA88" t="s">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="AB88">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC88" t="s">
-        <v>81</v>
+        <v>106</v>
       </c>
     </row>
     <row r="89" spans="18:36" x14ac:dyDescent="0.2">
-      <c r="R89" t="s">
-        <v>56</v>
-      </c>
-      <c r="S89" t="s">
-        <v>57</v>
-      </c>
-      <c r="T89">
-        <v>10</v>
-      </c>
-      <c r="V89" t="s">
-        <v>55</v>
-      </c>
-      <c r="W89" t="s">
-        <v>52</v>
-      </c>
-      <c r="AA89" t="s">
-        <v>105</v>
-      </c>
-      <c r="AB89">
-        <v>3</v>
-      </c>
-      <c r="AC89" t="s">
-        <v>106</v>
+      <c r="AD89" t="s">
+        <v>2</v>
+      </c>
+      <c r="AE89" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="90" spans="18:36" x14ac:dyDescent="0.2">
       <c r="AD90" t="s">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="AE90" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="91" spans="18:36" x14ac:dyDescent="0.2">
       <c r="AD91" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="AE91" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="92" spans="18:36" x14ac:dyDescent="0.2">
       <c r="AD92" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AE92" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="93" spans="18:36" x14ac:dyDescent="0.2">
       <c r="AD93" t="s">
-        <v>6</v>
+        <v>56</v>
       </c>
       <c r="AE93" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="94" spans="18:36" x14ac:dyDescent="0.2">
-      <c r="AD94" t="s">
-        <v>56</v>
-      </c>
-      <c r="AE94" t="s">
-        <v>111</v>
+      <c r="AF94">
+        <v>1</v>
+      </c>
+      <c r="AG94" t="s">
+        <v>112</v>
+      </c>
+      <c r="AH94">
+        <v>1</v>
+      </c>
+      <c r="AI94">
+        <v>1</v>
+      </c>
+      <c r="AJ94" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="95" spans="18:36" x14ac:dyDescent="0.2">
@@ -3522,7 +3523,7 @@
         <v>1</v>
       </c>
       <c r="AJ95" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
     </row>
     <row r="96" spans="18:36" x14ac:dyDescent="0.2">
@@ -3539,7 +3540,7 @@
         <v>1</v>
       </c>
       <c r="AJ96" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="97" spans="32:36" x14ac:dyDescent="0.2">
@@ -3553,10 +3554,10 @@
         <v>1</v>
       </c>
       <c r="AI97">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="AJ97" t="s">
-        <v>42</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98" spans="32:36" x14ac:dyDescent="0.2">
@@ -3570,10 +3571,10 @@
         <v>1</v>
       </c>
       <c r="AI98">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="AJ98" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="99" spans="32:36" x14ac:dyDescent="0.2">
@@ -3587,10 +3588,10 @@
         <v>1</v>
       </c>
       <c r="AI99">
+        <v>1</v>
+      </c>
+      <c r="AJ99" t="s">
         <v>8</v>
-      </c>
-      <c r="AJ99" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="100" spans="32:36" x14ac:dyDescent="0.2">
@@ -3607,7 +3608,7 @@
         <v>1</v>
       </c>
       <c r="AJ100" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
     </row>
     <row r="101" spans="32:36" x14ac:dyDescent="0.2">
@@ -3624,7 +3625,7 @@
         <v>1</v>
       </c>
       <c r="AJ101" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="102" spans="32:36" x14ac:dyDescent="0.2">
@@ -3641,7 +3642,7 @@
         <v>1</v>
       </c>
       <c r="AJ102" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="103" spans="32:36" x14ac:dyDescent="0.2">
@@ -3658,7 +3659,7 @@
         <v>1</v>
       </c>
       <c r="AJ103" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
     </row>
     <row r="104" spans="32:36" x14ac:dyDescent="0.2">
@@ -3672,10 +3673,10 @@
         <v>1</v>
       </c>
       <c r="AI104">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ104" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="105" spans="32:36" x14ac:dyDescent="0.2">
@@ -3689,10 +3690,10 @@
         <v>1</v>
       </c>
       <c r="AI105">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AJ105" t="s">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="106" spans="32:36" x14ac:dyDescent="0.2">
@@ -3706,27 +3707,27 @@
         <v>1</v>
       </c>
       <c r="AI106">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ106" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="107" spans="32:36" x14ac:dyDescent="0.2">
       <c r="AF107">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG107" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AH107">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI107">
         <v>2</v>
       </c>
       <c r="AJ107" t="s">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108" spans="32:36" x14ac:dyDescent="0.2">
@@ -3740,7 +3741,7 @@
         <v>2</v>
       </c>
       <c r="AI108">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ108" t="s">
         <v>1</v>
@@ -3757,7 +3758,7 @@
         <v>2</v>
       </c>
       <c r="AI109">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AJ109" t="s">
         <v>1</v>
@@ -3774,7 +3775,7 @@
         <v>2</v>
       </c>
       <c r="AI110">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AJ110" t="s">
         <v>1</v>
@@ -3791,7 +3792,7 @@
         <v>2</v>
       </c>
       <c r="AI111">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AJ111" t="s">
         <v>1</v>
@@ -3808,7 +3809,7 @@
         <v>2</v>
       </c>
       <c r="AI112">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AJ112" t="s">
         <v>1</v>
@@ -3816,33 +3817,33 @@
     </row>
     <row r="113" spans="32:36" x14ac:dyDescent="0.2">
       <c r="AF113">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG113" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AH113">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI113">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="AJ113" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="114" spans="32:36" x14ac:dyDescent="0.2">
       <c r="AF114">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG114" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AH114">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI114">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ114" t="s">
         <v>3</v>
@@ -3859,10 +3860,10 @@
         <v>4</v>
       </c>
       <c r="AI115">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AJ115" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="116" spans="32:36" x14ac:dyDescent="0.2">
@@ -3879,38 +3880,38 @@
         <v>1</v>
       </c>
       <c r="AJ116" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="117" spans="32:36" x14ac:dyDescent="0.2">
       <c r="AF117">
+        <v>5</v>
+      </c>
+      <c r="AG117" t="s">
+        <v>116</v>
+      </c>
+      <c r="AH117">
+        <v>5</v>
+      </c>
+      <c r="AI117">
         <v>4</v>
       </c>
-      <c r="AG117" t="s">
-        <v>115</v>
-      </c>
-      <c r="AH117">
-        <v>4</v>
-      </c>
-      <c r="AI117">
-        <v>1</v>
-      </c>
       <c r="AJ117" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="118" spans="32:36" x14ac:dyDescent="0.2">
       <c r="AF118">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG118" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AH118">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI118">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AJ118" t="s">
         <v>3</v>
@@ -3927,10 +3928,10 @@
         <v>6</v>
       </c>
       <c r="AI119">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AJ119" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="120" spans="32:36" x14ac:dyDescent="0.2">
@@ -3944,27 +3945,27 @@
         <v>6</v>
       </c>
       <c r="AI120">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AJ120" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="121" spans="32:36" x14ac:dyDescent="0.2">
       <c r="AF121">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG121" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AH121">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI121">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ121" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="122" spans="32:36" x14ac:dyDescent="0.2">
@@ -3978,27 +3979,27 @@
         <v>7</v>
       </c>
       <c r="AI122">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AJ122" t="s">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="123" spans="32:36" x14ac:dyDescent="0.2">
       <c r="AF123">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG123" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AH123">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI123">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AJ123" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="124" spans="32:36" x14ac:dyDescent="0.2">
@@ -4012,27 +4013,27 @@
         <v>8</v>
       </c>
       <c r="AI124">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AJ124" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
     </row>
     <row r="125" spans="32:36" x14ac:dyDescent="0.2">
       <c r="AF125">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG125" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AH125">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI125">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AJ125" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
     </row>
     <row r="126" spans="32:36" x14ac:dyDescent="0.2">
@@ -4046,27 +4047,27 @@
         <v>9</v>
       </c>
       <c r="AI126">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AJ126" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="127" spans="32:36" x14ac:dyDescent="0.2">
       <c r="AF127">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG127" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AH127">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AI127">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AJ127" t="s">
-        <v>1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="128" spans="32:36" x14ac:dyDescent="0.2">
@@ -4080,27 +4081,27 @@
         <v>10</v>
       </c>
       <c r="AI128">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AJ128" t="s">
-        <v>19</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129" spans="32:36" x14ac:dyDescent="0.2">
       <c r="AF129">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG129" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AH129">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AI129">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AJ129" t="s">
-        <v>1</v>
+        <v>34</v>
       </c>
     </row>
     <row r="130" spans="32:36" x14ac:dyDescent="0.2">
@@ -4114,27 +4115,27 @@
         <v>11</v>
       </c>
       <c r="AI130">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AJ130" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
     </row>
     <row r="131" spans="32:36" x14ac:dyDescent="0.2">
       <c r="AF131">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG131" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AH131">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AI131">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AJ131" t="s">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="132" spans="32:36" x14ac:dyDescent="0.2">
@@ -4148,27 +4149,27 @@
         <v>12</v>
       </c>
       <c r="AI132">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AJ132" t="s">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="133" spans="32:36" x14ac:dyDescent="0.2">
       <c r="AF133">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AG133" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AH133">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AI133">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AJ133" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="134" spans="32:36" x14ac:dyDescent="0.2">
@@ -4182,27 +4183,27 @@
         <v>13</v>
       </c>
       <c r="AI134">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AJ134" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
     </row>
     <row r="135" spans="32:36" x14ac:dyDescent="0.2">
       <c r="AF135">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AG135" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AH135">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AI135">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AJ135" t="s">
-        <v>35</v>
+        <v>1</v>
       </c>
     </row>
     <row r="136" spans="32:36" x14ac:dyDescent="0.2">
@@ -4216,27 +4217,27 @@
         <v>14</v>
       </c>
       <c r="AI136">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="AJ136" t="s">
-        <v>1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="137" spans="32:36" x14ac:dyDescent="0.2">
       <c r="AF137">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG137" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AH137">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AI137">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AJ137" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="138" spans="32:36" x14ac:dyDescent="0.2">
@@ -4253,38 +4254,38 @@
         <v>1</v>
       </c>
       <c r="AJ138" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="139" spans="32:36" x14ac:dyDescent="0.2">
       <c r="AF139">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG139" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AH139">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI139">
         <v>1</v>
       </c>
       <c r="AJ139" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="140" spans="32:36" x14ac:dyDescent="0.2">
       <c r="AF140">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AG140" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AH140">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AI140">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AJ140" t="s">
         <v>28</v>
@@ -4292,33 +4293,33 @@
     </row>
     <row r="141" spans="32:36" x14ac:dyDescent="0.2">
       <c r="AF141">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG141" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AH141">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AI141">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AJ141" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="142" spans="32:36" x14ac:dyDescent="0.2">
       <c r="AF142">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AG142" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AH142">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AI142">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AJ142" t="s">
         <v>33</v>
@@ -4326,16 +4327,16 @@
     </row>
     <row r="143" spans="32:36" x14ac:dyDescent="0.2">
       <c r="AF143">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AG143" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AH143">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AI143">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AJ143" t="s">
         <v>33</v>
@@ -4352,41 +4353,41 @@
         <v>20</v>
       </c>
       <c r="AI144">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AJ144" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="145" spans="32:36" x14ac:dyDescent="0.2">
       <c r="AF145">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG145" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AH145">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI145">
         <v>1</v>
       </c>
       <c r="AJ145" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
     </row>
     <row r="146" spans="32:36" x14ac:dyDescent="0.2">
       <c r="AF146">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG146" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AH146">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI146">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AJ146" t="s">
         <v>34</v>
@@ -4394,33 +4395,33 @@
     </row>
     <row r="147" spans="32:36" x14ac:dyDescent="0.2">
       <c r="AF147">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG147" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AH147">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI147">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AJ147" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="148" spans="32:36" x14ac:dyDescent="0.2">
       <c r="AF148">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AG148" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AH148">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI148">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AJ148" t="s">
         <v>35</v>
@@ -4428,19 +4429,19 @@
     </row>
     <row r="149" spans="32:36" x14ac:dyDescent="0.2">
       <c r="AF149">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AG149" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AH149">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI149">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AJ149" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
     </row>
     <row r="150" spans="32:36" x14ac:dyDescent="0.2">
@@ -4454,27 +4455,27 @@
         <v>25</v>
       </c>
       <c r="AI150">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AJ150" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="151" spans="32:36" x14ac:dyDescent="0.2">
       <c r="AF151">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG151" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AH151">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI151">
         <v>2</v>
       </c>
       <c r="AJ151" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="152" spans="32:36" x14ac:dyDescent="0.2">
@@ -4488,27 +4489,27 @@
         <v>26</v>
       </c>
       <c r="AI152">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AJ152" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="153" spans="32:36" x14ac:dyDescent="0.2">
       <c r="AF153">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG153" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AH153">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI153">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AJ153" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="154" spans="32:36" x14ac:dyDescent="0.2">
@@ -4522,27 +4523,27 @@
         <v>27</v>
       </c>
       <c r="AI154">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AJ154" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="155" spans="32:36" x14ac:dyDescent="0.2">
       <c r="AF155">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AG155" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AH155">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AI155">
         <v>4</v>
       </c>
       <c r="AJ155" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="156" spans="32:36" x14ac:dyDescent="0.2">
@@ -4556,41 +4557,41 @@
         <v>28</v>
       </c>
       <c r="AI156">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AJ156" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="157" spans="32:36" x14ac:dyDescent="0.2">
       <c r="AF157">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AG157" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AH157">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AI157">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AJ157" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="158" spans="32:36" x14ac:dyDescent="0.2">
       <c r="AF158">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AG158" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AH158">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AI158">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ158" t="s">
         <v>40</v>
@@ -4598,16 +4599,16 @@
     </row>
     <row r="159" spans="32:36" x14ac:dyDescent="0.2">
       <c r="AF159">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AG159" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AH159">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AI159">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ159" t="s">
         <v>40</v>
@@ -4615,16 +4616,16 @@
     </row>
     <row r="160" spans="32:36" x14ac:dyDescent="0.2">
       <c r="AF160">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AG160" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AH160">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AI160">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AJ160" t="s">
         <v>40</v>
@@ -4641,27 +4642,27 @@
         <v>32</v>
       </c>
       <c r="AI161">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AJ161" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
     </row>
     <row r="162" spans="32:36" x14ac:dyDescent="0.2">
       <c r="AF162">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AG162" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AH162">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AI162">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ162" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="163" spans="32:36" x14ac:dyDescent="0.2">
@@ -4675,10 +4676,10 @@
         <v>33</v>
       </c>
       <c r="AI163">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AJ163" t="s">
-        <v>3</v>
+        <v>40</v>
       </c>
     </row>
     <row r="164" spans="32:36" x14ac:dyDescent="0.2">
@@ -4692,27 +4693,27 @@
         <v>33</v>
       </c>
       <c r="AI164">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AJ164" t="s">
-        <v>40</v>
+        <v>13</v>
       </c>
     </row>
     <row r="165" spans="32:36" x14ac:dyDescent="0.2">
       <c r="AF165">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AG165" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AH165">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AI165">
         <v>2</v>
       </c>
       <c r="AJ165" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
     </row>
     <row r="166" spans="32:36" x14ac:dyDescent="0.2">
@@ -4729,24 +4730,24 @@
         <v>2</v>
       </c>
       <c r="AJ166" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="167" spans="32:36" x14ac:dyDescent="0.2">
       <c r="AF167">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AG167" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AH167">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AI167">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AJ167" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
     </row>
     <row r="168" spans="32:36" x14ac:dyDescent="0.2">
@@ -4760,10 +4761,10 @@
         <v>35</v>
       </c>
       <c r="AI168">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AJ168" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="169" spans="32:36" x14ac:dyDescent="0.2">
@@ -4777,10 +4778,10 @@
         <v>35</v>
       </c>
       <c r="AI169">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AJ169" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
     </row>
     <row r="170" spans="32:36" x14ac:dyDescent="0.2">
@@ -4797,24 +4798,24 @@
         <v>1</v>
       </c>
       <c r="AJ170" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="171" spans="32:36" x14ac:dyDescent="0.2">
       <c r="AF171">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="AG171" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AH171">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="AI171">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AJ171" t="s">
-        <v>44</v>
+        <v>3</v>
       </c>
     </row>
     <row r="172" spans="32:36" x14ac:dyDescent="0.2">
@@ -4828,27 +4829,27 @@
         <v>36</v>
       </c>
       <c r="AI172">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AJ172" t="s">
-        <v>3</v>
+        <v>49</v>
       </c>
     </row>
     <row r="173" spans="32:36" x14ac:dyDescent="0.2">
       <c r="AF173">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AG173" t="s">
-        <v>147</v>
+        <v>80</v>
       </c>
       <c r="AH173">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AI173">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ173" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="174" spans="32:36" x14ac:dyDescent="0.2">
@@ -4865,7 +4866,7 @@
         <v>2</v>
       </c>
       <c r="AJ174" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="175" spans="32:36" x14ac:dyDescent="0.2">
@@ -4882,7 +4883,7 @@
         <v>2</v>
       </c>
       <c r="AJ175" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="176" spans="32:36" x14ac:dyDescent="0.2">
@@ -4899,7 +4900,7 @@
         <v>2</v>
       </c>
       <c r="AJ176" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="177" spans="32:36" x14ac:dyDescent="0.2">
@@ -4913,10 +4914,10 @@
         <v>37</v>
       </c>
       <c r="AI177">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AJ177" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="178" spans="32:36" x14ac:dyDescent="0.2">
@@ -4930,10 +4931,10 @@
         <v>37</v>
       </c>
       <c r="AI178">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ178" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
     </row>
     <row r="179" spans="32:36" x14ac:dyDescent="0.2">
@@ -4950,7 +4951,7 @@
         <v>2</v>
       </c>
       <c r="AJ179" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
     </row>
     <row r="180" spans="32:36" x14ac:dyDescent="0.2">
@@ -4967,7 +4968,7 @@
         <v>2</v>
       </c>
       <c r="AJ180" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="181" spans="32:36" x14ac:dyDescent="0.2">
@@ -4984,7 +4985,7 @@
         <v>2</v>
       </c>
       <c r="AJ181" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="182" spans="32:36" x14ac:dyDescent="0.2">
@@ -5001,7 +5002,7 @@
         <v>2</v>
       </c>
       <c r="AJ182" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="183" spans="32:36" x14ac:dyDescent="0.2">
@@ -5018,7 +5019,7 @@
         <v>2</v>
       </c>
       <c r="AJ183" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
     </row>
     <row r="184" spans="32:36" x14ac:dyDescent="0.2">
@@ -5035,7 +5036,7 @@
         <v>2</v>
       </c>
       <c r="AJ184" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
     </row>
     <row r="185" spans="32:36" x14ac:dyDescent="0.2">
@@ -5049,10 +5050,10 @@
         <v>37</v>
       </c>
       <c r="AI185">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AJ185" t="s">
-        <v>25</v>
+        <v>3</v>
       </c>
     </row>
     <row r="186" spans="32:36" x14ac:dyDescent="0.2">
@@ -5066,27 +5067,27 @@
         <v>37</v>
       </c>
       <c r="AI186">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AJ186" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="187" spans="32:36" x14ac:dyDescent="0.2">
       <c r="AF187">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AG187" t="s">
-        <v>80</v>
+        <v>148</v>
       </c>
       <c r="AH187">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AI187">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AJ187" t="s">
-        <v>1</v>
+        <v>51</v>
       </c>
     </row>
     <row r="188" spans="32:36" x14ac:dyDescent="0.2">
@@ -5100,36 +5101,19 @@
         <v>38</v>
       </c>
       <c r="AI188">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AJ188" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="189" spans="32:36" x14ac:dyDescent="0.2">
-      <c r="AF189">
-        <v>38</v>
-      </c>
-      <c r="AG189" t="s">
-        <v>148</v>
-      </c>
-      <c r="AH189">
-        <v>38</v>
-      </c>
-      <c r="AI189">
-        <v>1</v>
-      </c>
-      <c r="AJ189" t="s">
         <v>50</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:AT206">
-    <sortCondition ref="A1:A206"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:AT205">
+    <sortCondition ref="A1:A205"/>
   </sortState>
   <mergeCells count="2">
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A51:C51"/>
+    <mergeCell ref="A50:C50"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup scale="65" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="10"/>
